--- a/Documents/Product Catalog/Office/Training Chair.xlsx
+++ b/Documents/Product Catalog/Office/Training Chair.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\Office\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6579576E-A94C-4FB1-B8DF-5FE8921BA42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{153A3B40-58CF-4E1E-9ADC-98D55A9EB087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1692,10 +1692,10 @@
       </c>
       <c r="L7" s="8">
         <f t="shared" si="0"/>
-        <v>4320</v>
+        <v>4050</v>
       </c>
       <c r="M7" s="6">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="N7" s="7">
         <v>0.1</v>
@@ -1744,10 +1744,10 @@
       </c>
       <c r="L8" s="8">
         <f t="shared" si="0"/>
-        <v>5220</v>
+        <v>4680</v>
       </c>
       <c r="M8" s="6">
-        <v>5800</v>
+        <v>5200</v>
       </c>
       <c r="N8" s="7">
         <v>0.1</v>
@@ -1796,10 +1796,10 @@
       </c>
       <c r="L9" s="8">
         <f t="shared" si="0"/>
-        <v>9450</v>
+        <v>9720</v>
       </c>
       <c r="M9" s="6">
-        <v>10500</v>
+        <v>10800</v>
       </c>
       <c r="N9" s="7">
         <v>0.1</v>
